--- a/objectives/mastery-objectives.xlsx
+++ b/objectives/mastery-objectives.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Course Repo: gh-pr-mastery</t>
+          <t>Course Repo: perro-ruidoso/gh-pr-mastery</t>
         </is>
       </c>
     </row>

--- a/objectives/mastery-objectives.xlsx
+++ b/objectives/mastery-objectives.xlsx
@@ -919,7 +919,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Express work dependencies as sub-issues and blocking relations via the gh CLI, and render the resulting graph as a Mermaid diagram.</t>
+          <t>Record work dependencies as GitHub issue dependencies via the gh CLI, distinguish them from sub-issues and say why a sub-issue cannot express a two-parent join, and render the resulting graph as a Mermaid diagram.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>GitHub Docs: Adding sub-issues</t>
+          <t>GitHub Docs: Issue dependencies REST API; Adding sub-issues</t>
         </is>
       </c>
     </row>

--- a/objectives/mastery-objectives.xlsx
+++ b/objectives/mastery-objectives.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery Objectives" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mastery Objectives'!$A$1:$H$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mastery Objectives'!$A$1:$I$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="5">
@@ -67,12 +71,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -443,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -454,6 +461,7 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,6 +505,11 @@
           <t>Primary Source</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Learning Pages</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -537,6 +550,12 @@
           <t>GitHub Docs: Creating a repository from a template</t>
         </is>
       </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Your Instance and Your Toolchain - docs/week-01/m01-instance-and-toolchain/index.html
+Create Your Instance - docs/week-01/m01-instance-and-toolchain/create-your-instance.html</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -577,6 +596,12 @@
           <t>GitHub Docs: About pull requests</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Two Refs and a Conversation - docs/week-01/m02-what-a-pull-request-is/index.html
+Heads, Forks, and Drafts - docs/week-01/m02-what-a-pull-request-is/heads-forks-and-drafts.html</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -617,6 +642,12 @@
           <t>GitHub Docs: About comparing branches in pull requests</t>
         </is>
       </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>The Merge Base - docs/week-01/m03-the-merge-base/index.html
+What GitHub Shows You - docs/week-01/m03-the-merge-base/what-github-shows.html</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -657,6 +688,12 @@
           <t>GitHub CLI manual: gh pr, gh issue</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Listing and Viewing - docs/week-01/m04-reading-work-from-the-terminal/index.html
+Filter and Diff - docs/week-01/m04-reading-work-from-the-terminal/filter-and-diff.html</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -697,6 +734,12 @@
           <t>mattpocock/skills: setup-matt-pocock-skills</t>
         </is>
       </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Teaching Your Repo to the Skills - docs/week-01/m05-configuring-the-skills/index.html
+Labels and Domain Docs - docs/week-01/m05-configuring-the-skills/labels-and-domain-docs.html</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -737,244 +780,281 @@
           <t>Course Repo: perro-ruidoso/gh-pr-mastery</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Reading the Exhibit - docs/week-01/m06-reading-the-exhibit/index.html
+The Method - docs/week-01/m06-reading-the-exhibit/the-method.html
+Your Target - docs/week-01/m06-reading-the-exhibit/your-target.html</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>M07</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Issues as units of agent work</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Issues</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Write an issue body a fresh agent session can execute without asking a question: context, acceptance criteria, and explicit out-of-scope.</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Create</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>A2 (rubric)</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>GitHub Docs: About issues</t>
         </is>
       </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>M08</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Issues as units of agent work</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Issues</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Apply labels, issue types, and issue templates so a backlog is filterable and ready work is findable.</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>A2 (checker)</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>GitHub Docs: Labels; Issue types; Issue templates</t>
         </is>
       </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>M09</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Issues as units of agent work</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Turn a design conversation into a published spec issue with /to-spec, and check the result before filing.</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>A2 (checker)</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>mattpocock/skills: to-spec</t>
         </is>
       </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>M10</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Issues as units of agent work</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Decomposition</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Decompose a spec into 6-10 tracer-bullet tickets with declared blocking edges using /to-tickets.</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Create</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>A2 (rubric)</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>mattpocock/skills: to-tickets</t>
         </is>
       </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>M11</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Issues as units of agent work</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Work dependencies</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Record work dependencies as GitHub issue dependencies via the gh CLI, distinguish them from sub-issues and say why a sub-issue cannot express a two-parent join, and render the resulting graph as a Mermaid diagram.</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>A2 (checker)</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>GitHub Docs: Issue dependencies REST API; Adding sub-issues</t>
         </is>
       </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>M12</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Issues as units of agent work</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>PM integration</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Connect Linear to the Instance and verify that issues and PRs appear and update without manual touching.</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>A2 (checker)</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Linear Docs: GitHub integration</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1017,6 +1097,11 @@
           <t>GitHub CLI manual: gh issue develop</t>
         </is>
       </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1057,6 +1142,11 @@
           <t>Course exercise</t>
         </is>
       </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1097,6 +1187,11 @@
           <t>GitHub Docs: Linking a pull request to an issue</t>
         </is>
       </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1137,6 +1232,11 @@
           <t>GitHub Docs: Changing the base branch of a pull request</t>
         </is>
       </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1177,6 +1277,11 @@
           <t>mattpocock/skills: resolving-merge-conflicts</t>
         </is>
       </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1217,244 +1322,279 @@
           <t>mattpocock/skills repo</t>
         </is>
       </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>M19</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Owning the diff</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Review mechanics</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Distinguish a single comment, a review, and a suggested change; batch comments and submit a review with a verdict.</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>A4 (checker)</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>GitHub Docs: Reviewing proposed changes in a pull request</t>
         </is>
       </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>M20</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Owning the diff</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Review mechanics</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Resolve conversations, re-request review, and read a PR's review state correctly.</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>A4 (checker)</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>GitHub Docs: Commenting on a pull request</t>
         </is>
       </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>M21</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Owning the diff</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Agentic review</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Run /code-review on a branch and separate verified findings from noise across its Standards and Spec axes.</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Analyze</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>A4 (written)</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>code.claude.com: Code Review</t>
         </is>
       </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>M22</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Owning the diff</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Write review comments a peer can act on without asking a clarifying question: located, specific, and severity-marked.</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Create</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>A4 paired (rubric)</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Course exercise</t>
         </is>
       </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>M23</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Owning the diff</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Authoring</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Respond to review as the author: direct Claude to address findings, push, and re-request review without losing the thread.</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>A4 paired (checker)</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Course exercise</t>
         </is>
       </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>M24</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Owning the diff</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Bug capture</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Turn what review uncovers into filed issues with /qa rather than fixing out of scope in the open PR.</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>A4 (checker)</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>mattpocock/skills: qa</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1497,6 +1637,11 @@
           <t>GitHub Docs: About continuous integration with GitHub Actions</t>
         </is>
       </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1537,6 +1682,11 @@
           <t>GitHub Docs: About rulesets; About protected branches</t>
         </is>
       </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1577,6 +1727,11 @@
           <t>GitHub Docs: About code owners</t>
         </is>
       </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1617,6 +1772,11 @@
           <t>GitHub Docs: About merge methods on GitHub</t>
         </is>
       </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1657,6 +1817,11 @@
           <t>GitHub Docs: Managing a merge queue</t>
         </is>
       </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1697,249 +1862,292 @@
           <t>code.claude.com: GitHub Actions; GitHub Docs: Using secrets in GitHub Actions</t>
         </is>
       </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>M31</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>The maintainer seat, PM integration, and capstone</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Forks</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Contribute to the Upstream Repo from a fork: sync the fork, open a cross-repo PR, and follow the repo's contribution etiquette.</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>A6 (checker)</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>GitHub Docs: About forks; Contributing to a project</t>
         </is>
       </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>M32</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>The maintainer seat, PM integration, and capstone</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Maintainer seat</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Triage incoming external PRs and issues through the five-label state machine with /triage, writing agent-ready briefs.</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>A6 (rubric)</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>mattpocock/skills: triage</t>
         </is>
       </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>M33</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>The maintainer seat, PM integration, and capstone</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>PM integration</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Contrast Linear's model - teams, projects, cycles - with GitHub's repos, issues, and milestones, and name where the two disagree.</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>Understand</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>Quiz 2</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>Linear Docs; GitHub Docs: About milestones</t>
         </is>
       </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>M34</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>The maintainer seat, PM integration, and capstone</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>PM integration</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Drive issue status from git activity: branch names, magic words, and PR state transitions, with no manual status changes.</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>A6 (checker)</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>Linear Docs: GitHub integration</t>
         </is>
       </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>M35</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n">
+      <c r="B36" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>The maintainer seat, PM integration, and capstone</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Judgment</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Decide where the source of truth for work should live for a given team, and defend it against duplication, sync lag, and permissions.</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>Evaluate</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>Quiz 2; Capstone</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>Course exercise</t>
         </is>
       </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>M36</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>The maintainer seat, PM integration, and capstone</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Synthesis</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>Ship one complete loop end to end and write a Personal PR Workflow Playbook naming the gates and defaults you will carry to your own work.</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>Create</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>Capstone</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>Course project</t>
         </is>
       </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H37"/>
+  <autoFilter ref="A1:I37"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/objectives/mastery-objectives.xlsx
+++ b/objectives/mastery-objectives.xlsx
@@ -71,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -83,6 +83,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -827,9 +830,10 @@
           <t>GitHub Docs: About issues</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>The Ticket as a Contract - docs/week-02/m07-issues-an-agent-can-execute/index.html
+Criteria That Can Fail - docs/week-02/m07-issues-an-agent-can-execute/acceptance-criteria.html</t>
         </is>
       </c>
     </row>
@@ -872,9 +876,10 @@
           <t>GitHub Docs: Labels; Issue types; Issue templates</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Labels and Issue Types - docs/week-02/m08-labels-types-and-templates/index.html
+Issue Templates - docs/week-02/m08-labels-types-and-templates/issue-templates.html</t>
         </is>
       </c>
     </row>
@@ -917,9 +922,10 @@
           <t>mattpocock/skills: to-spec</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>From Conversation to Spec - docs/week-02/m09-conversation-to-spec/index.html
+Checking the Spec - docs/week-02/m09-conversation-to-spec/checking-the-spec.html</t>
         </is>
       </c>
     </row>
@@ -962,9 +968,10 @@
           <t>mattpocock/skills: to-tickets</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Tracer Bullets and Blocking Edges - docs/week-02/m10-decomposing-into-tickets/index.html
+Reading the Seed Backlog - docs/week-02/m10-decomposing-into-tickets/the-seed-backlog.html</t>
         </is>
       </c>
     </row>
@@ -1007,9 +1014,10 @@
           <t>GitHub Docs: Issue dependencies REST API; Adding sub-issues</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Two Features, Two Shapes - docs/week-02/m11-recording-dependencies/index.html
+Reading the Graph Back - docs/week-02/m11-recording-dependencies/reading-the-graph-back.html</t>
         </is>
       </c>
     </row>
@@ -1052,9 +1060,10 @@
           <t>Linear Docs: GitHub integration</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Linear Above GitHub - docs/week-02/m12-wiring-linear/index.html
+Verify Without Touching - docs/week-02/m12-wiring-linear/verify-without-touching.html</t>
         </is>
       </c>
     </row>
@@ -2147,6 +2156,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/objectives/mastery-objectives.xlsx
+++ b/objectives/mastery-objectives.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>GitHub Docs: Issue dependencies REST API; Adding sub-issues</t>
+          <t>GitHub Docs: Creating issue dependencies; Adding sub-issues; Issue dependencies REST API</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">

--- a/objectives/mastery-objectives.xlsx
+++ b/objectives/mastery-objectives.xlsx
@@ -71,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -83,6 +83,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -827,9 +830,10 @@
           <t>GitHub Docs: About issues</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>The Ticket as a Contract - docs/week-02/m07-issues-an-agent-can-execute/index.html
+Criteria That Can Fail - docs/week-02/m07-issues-an-agent-can-execute/acceptance-criteria.html</t>
         </is>
       </c>
     </row>
@@ -872,9 +876,10 @@
           <t>GitHub Docs: Labels; Issue types; Issue templates</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Labels and Issue Types - docs/week-02/m08-labels-types-and-templates/index.html
+Issue Templates - docs/week-02/m08-labels-types-and-templates/issue-templates.html</t>
         </is>
       </c>
     </row>
@@ -917,9 +922,10 @@
           <t>mattpocock/skills: to-spec</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>From Conversation to Spec - docs/week-02/m09-conversation-to-spec/index.html
+Checking the Spec - docs/week-02/m09-conversation-to-spec/checking-the-spec.html</t>
         </is>
       </c>
     </row>
@@ -962,9 +968,10 @@
           <t>mattpocock/skills: to-tickets</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Tracer Bullets and Blocking Edges - docs/week-02/m10-decomposing-into-tickets/index.html
+Reading the Seed Backlog - docs/week-02/m10-decomposing-into-tickets/the-seed-backlog.html</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1011,13 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>GitHub Docs: Issue dependencies REST API; Adding sub-issues</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>GitHub Docs: Creating issue dependencies; Adding sub-issues; Issue dependencies REST API</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Two Features, Two Shapes - docs/week-02/m11-recording-dependencies/index.html
+Reading the Graph Back - docs/week-02/m11-recording-dependencies/reading-the-graph-back.html</t>
         </is>
       </c>
     </row>
@@ -1052,9 +1060,10 @@
           <t>Linear Docs: GitHub integration</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Linear Above GitHub - docs/week-02/m12-wiring-linear/index.html
+Verify Without Touching - docs/week-02/m12-wiring-linear/verify-without-touching.html</t>
         </is>
       </c>
     </row>
@@ -2147,6 +2156,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/objectives/mastery-objectives.xlsx
+++ b/objectives/mastery-objectives.xlsx
@@ -1106,9 +1106,10 @@
           <t>GitHub CLI manual: gh issue develop</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>A Branch Bound to an Issue - docs/week-03/m13-branch-per-issue/index.html
+Naming That Links Twice - docs/week-03/m13-branch-per-issue/naming-that-links.html</t>
         </is>
       </c>
     </row>
@@ -1151,9 +1152,10 @@
           <t>Course exercise</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>What a Reviewable Diff Looks Like - docs/week-03/m14-reviewable-diffs/index.html
+Splitting a Drive-by - docs/week-03/m14-reviewable-diffs/splitting-a-drive-by.html</t>
         </is>
       </c>
     </row>
@@ -1196,9 +1198,10 @@
           <t>GitHub Docs: Linking a pull request to an issue</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Intent, Scope, Verification, Risk - docs/week-03/m15-the-pr-body/index.html
+The Keyword and Its Two Conditions - docs/week-03/m15-the-pr-body/the-closing-keyword.html</t>
         </is>
       </c>
     </row>
@@ -1241,9 +1244,11 @@
           <t>GitHub Docs: Changing the base branch of a pull request</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Stacking on a Branch That Is Not Main - docs/week-03/m16-stacked-prs/index.html
+Retarget, Then Look Again - docs/week-03/m16-stacked-prs/retargeting.html
+What Deleting the Parent Does - docs/week-03/m16-stacked-prs/deleting-the-parent.html</t>
         </is>
       </c>
     </row>
@@ -1286,9 +1291,10 @@
           <t>mattpocock/skills: resolving-merge-conflicts</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Where the Conflict Came From - docs/week-03/m17-resolving-conflicts/index.html
+Running /resolving-merge-conflicts - docs/week-03/m17-resolving-conflicts/running-the-skill.html</t>
         </is>
       </c>
     </row>
@@ -1331,9 +1337,10 @@
           <t>mattpocock/skills repo</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Ask Matt First - docs/week-03/m18-the-toolbelt/index.html
+Six Skills, Six Situations - docs/week-03/m18-the-toolbelt/six-skills-six-situations.html</t>
         </is>
       </c>
     </row>
@@ -2162,6 +2169,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/objectives/mastery-objectives.xlsx
+++ b/objectives/mastery-objectives.xlsx
@@ -1383,9 +1383,10 @@
           <t>GitHub Docs: Reviewing proposed changes in a pull request</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Three Things That Look Alike - docs/week-04/m19-comments-reviews-suggestions/index.html
+A Batched Review from gh - docs/week-04/m19-comments-reviews-suggestions/batching-from-the-terminal.html</t>
         </is>
       </c>
     </row>
@@ -1428,9 +1429,10 @@
           <t>GitHub Docs: Commenting on a pull request</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Threads, Resolution, Re-request - docs/week-04/m20-review-state/index.html
+Reading reviewDecision Correctly - docs/week-04/m20-review-state/reading-the-state.html</t>
         </is>
       </c>
     </row>
@@ -1473,9 +1475,11 @@
           <t>code.claude.com: Code Review</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Two /code-reviews, Two Axes - docs/week-04/m21-code-review/index.html
+The Output, Unedited - docs/week-04/m21-code-review/the-output-verbatim.html
+From Findings to Verdicts - docs/week-04/m21-code-review/findings-to-verdicts.html</t>
         </is>
       </c>
     </row>
@@ -1518,9 +1522,10 @@
           <t>Course exercise</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Located, Specific, Severity-Marked - docs/week-04/m22-comments-a-peer-can-act-on/index.html
+Severity Words and the Comments That Force a Question - docs/week-04/m22-comments-a-peer-can-act-on/severity-and-anti-patterns.html</t>
         </is>
       </c>
     </row>
@@ -1563,9 +1568,10 @@
           <t>Course exercise</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Direct Claude, Push, Reply - docs/week-04/m23-answering-review/index.html
+Re-request Without Losing the Thread - docs/week-04/m23-answering-review/re-requesting-review.html</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1611,13 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>mattpocock/skills: qa</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>mattpocock/skills: qa (vendored by the course - removed upstream 2026-08-05)</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Out of Scope Means an Issue, Not a Commit - docs/week-04/m24-filing-what-review-uncovers/index.html
+What /qa Writes, and What It Does Not - docs/week-04/m24-filing-what-review-uncovers/what-qa-writes.html</t>
         </is>
       </c>
     </row>
@@ -2175,6 +2182,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
